--- a/templates/Haftalik-Calisma_Plani_10-16_Agustos.xlsx
+++ b/templates/Haftalik-Calisma_Plani_10-16_Agustos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aytedu\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Puantaj_Yeni\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54609BDC-1616-4416-88D7-B9925BB354E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF1AFC7-D485-4303-9332-60B2ED6F0B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="65">
   <si>
     <t>HAFTALIK ÇALIŞMA PLANI</t>
   </si>
@@ -120,9 +120,6 @@
     <t>HARUN ARSLANTAŞ</t>
   </si>
   <si>
-    <t>1 GÜN ALACAK İZNİ OLDU</t>
-  </si>
-  <si>
     <t>GÖKHAN KAYA</t>
   </si>
   <si>
@@ -142,9 +139,6 @@
   </si>
   <si>
     <t>Aİ</t>
-  </si>
-  <si>
-    <t>1 gün borçlu idi</t>
   </si>
   <si>
     <t>YAKUP YILMAZ</t>
@@ -371,7 +365,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -417,12 +411,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
       </patternFill>
     </fill>
@@ -444,14 +432,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="26">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -682,19 +664,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -705,21 +674,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
@@ -766,6 +720,114 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -777,13 +839,12 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="5" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="11" fillId="8" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -795,81 +856,46 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="10" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -878,29 +904,91 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -910,76 +998,57 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="30" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="27" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="27" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="27" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="14" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="5" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1276,31 +1345,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="78"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="44"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -1320,1262 +1389,1224 @@
       <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="81"/>
+      <c r="B3" s="47"/>
       <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="85"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="48">
         <v>46244</v>
       </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="69">
+      <c r="E4" s="49"/>
+      <c r="F4" s="48">
         <v>46245</v>
       </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="69">
+      <c r="G4" s="49"/>
+      <c r="H4" s="48">
         <v>46246</v>
       </c>
-      <c r="I4" s="70"/>
-      <c r="J4" s="69">
+      <c r="I4" s="49"/>
+      <c r="J4" s="48">
         <v>46247</v>
       </c>
-      <c r="K4" s="70"/>
-      <c r="L4" s="69">
+      <c r="K4" s="49"/>
+      <c r="L4" s="48">
         <v>46248</v>
       </c>
-      <c r="M4" s="70"/>
-      <c r="N4" s="69">
+      <c r="M4" s="49"/>
+      <c r="N4" s="48">
         <v>46249</v>
       </c>
-      <c r="O4" s="70"/>
-      <c r="P4" s="69">
+      <c r="O4" s="49"/>
+      <c r="P4" s="48">
         <v>46250</v>
       </c>
-      <c r="Q4" s="70"/>
-      <c r="R4" s="71" t="s">
+      <c r="Q4" s="49"/>
+      <c r="R4" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="S4" s="72"/>
+      <c r="S4" s="51"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="73"/>
-      <c r="B5" s="74" t="s">
+      <c r="A5" s="82"/>
+      <c r="B5" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67" t="s">
+      <c r="E5" s="54"/>
+      <c r="F5" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67" t="s">
+      <c r="G5" s="54"/>
+      <c r="H5" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67" t="s">
+      <c r="I5" s="54"/>
+      <c r="J5" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67" t="s">
+      <c r="K5" s="54"/>
+      <c r="L5" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67" t="s">
+      <c r="M5" s="54"/>
+      <c r="N5" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67" t="s">
+      <c r="O5" s="54"/>
+      <c r="P5" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="84" t="s">
-        <v>66</v>
-      </c>
-      <c r="S5" s="84"/>
-    </row>
-    <row r="6" spans="1:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="73"/>
-      <c r="B6" s="74"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="8" t="s">
+      <c r="Q5" s="58"/>
+      <c r="R5" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" s="80"/>
+    </row>
+    <row r="6" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="82"/>
+      <c r="B6" s="71"/>
+      <c r="C6" s="72"/>
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="P6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="84"/>
-      <c r="S6" s="84"/>
-    </row>
-    <row r="7" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+      <c r="R6" s="79"/>
+      <c r="S6" s="80"/>
+    </row>
+    <row r="7" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="77">
         <v>1</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="81" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="15"/>
-      <c r="N7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" s="15"/>
-      <c r="P7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q7" s="17"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="56"/>
-    </row>
-    <row r="8" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="D7" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="11"/>
+      <c r="N7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="11"/>
+      <c r="P7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="57"/>
+    </row>
+    <row r="8" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="78">
         <v>2</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15" t="s">
+      <c r="E8" s="11"/>
+      <c r="F8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15" t="s">
+      <c r="G8" s="11"/>
+      <c r="H8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15" t="s">
+      <c r="I8" s="11"/>
+      <c r="J8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15" t="s">
+      <c r="K8" s="11"/>
+      <c r="L8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15" t="s">
+      <c r="M8" s="11"/>
+      <c r="N8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="O8" s="15"/>
-      <c r="P8" s="19" t="s">
+      <c r="O8" s="11"/>
+      <c r="P8" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="56"/>
-    </row>
-    <row r="9" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A9" s="11">
+      <c r="Q8" s="13"/>
+      <c r="R8" s="56"/>
+      <c r="S8" s="57"/>
+    </row>
+    <row r="9" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="77">
         <v>3</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="19" t="s">
+      <c r="D9" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="15"/>
-      <c r="N9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9" s="15"/>
-      <c r="P9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="56"/>
-    </row>
-    <row r="10" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="M9" s="11"/>
+      <c r="N9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="11"/>
+      <c r="P9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="56"/>
+      <c r="S9" s="57"/>
+    </row>
+    <row r="10" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="78">
         <v>4</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="16" t="s">
+      <c r="E10" s="11"/>
+      <c r="F10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16" t="s">
+      <c r="G10" s="11"/>
+      <c r="H10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="16" t="s">
+      <c r="I10" s="11"/>
+      <c r="J10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="16" t="s">
+      <c r="K10" s="11"/>
+      <c r="L10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="15"/>
-      <c r="N10" s="16" t="s">
+      <c r="M10" s="11"/>
+      <c r="N10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="O10" s="15"/>
-      <c r="P10" s="19" t="s">
+      <c r="O10" s="11"/>
+      <c r="P10" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="56"/>
-    </row>
-    <row r="11" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+      <c r="Q10" s="13"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="57"/>
+    </row>
+    <row r="11" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="77">
         <v>5</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" s="15"/>
-      <c r="N11" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11" s="15"/>
-      <c r="P11" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="55"/>
-      <c r="S11" s="56"/>
-    </row>
-    <row r="12" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
+      <c r="E11" s="11"/>
+      <c r="F11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="11"/>
+      <c r="N11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11" s="11"/>
+      <c r="P11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="57"/>
+    </row>
+    <row r="12" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="78">
         <v>6</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="19" t="s">
+      <c r="D12" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" s="15"/>
-      <c r="N12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12" s="15"/>
-      <c r="P12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="55" t="s">
+      <c r="I12" s="11"/>
+      <c r="J12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="11"/>
+      <c r="N12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="57"/>
+    </row>
+    <row r="13" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="77">
+        <v>7</v>
+      </c>
+      <c r="B13" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="S12" s="56"/>
-    </row>
-    <row r="13" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="11">
-        <v>7</v>
-      </c>
-      <c r="B13" s="12" t="s">
+      <c r="C13" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" s="11"/>
+      <c r="N13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13" s="11"/>
+      <c r="P13" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="57"/>
+      <c r="T13" s="55"/>
+      <c r="U13" s="55"/>
+      <c r="V13" s="55"/>
+    </row>
+    <row r="14" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="78">
+        <v>8</v>
+      </c>
+      <c r="B14" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M13" s="15"/>
-      <c r="N13" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13" s="15"/>
-      <c r="P13" s="19" t="s">
+      <c r="C14" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="11"/>
+      <c r="H14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="11"/>
+      <c r="N14" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="56"/>
-      <c r="T13" s="65"/>
-      <c r="U13" s="66"/>
-      <c r="V13" s="66"/>
-    </row>
-    <row r="14" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
-        <v>8</v>
-      </c>
-      <c r="B14" s="21" t="s">
+      <c r="O14" s="11"/>
+      <c r="P14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="57"/>
+    </row>
+    <row r="15" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="77">
+        <v>9</v>
+      </c>
+      <c r="B15" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M14" s="15"/>
-      <c r="N14" s="19" t="s">
+      <c r="C15" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="O14" s="15"/>
-      <c r="P14" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="55"/>
-      <c r="S14" s="56"/>
-    </row>
-    <row r="15" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
-        <v>9</v>
-      </c>
-      <c r="B15" s="22" t="s">
+      <c r="E15" s="11"/>
+      <c r="F15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="11"/>
+      <c r="N15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15" s="11"/>
+      <c r="P15" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="57"/>
+      <c r="T15" s="59"/>
+      <c r="U15" s="59"/>
+      <c r="V15" s="59"/>
+    </row>
+    <row r="16" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="78">
+        <v>10</v>
+      </c>
+      <c r="B16" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="19" t="s">
+      <c r="C16" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O15" s="15"/>
-      <c r="P15" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="56"/>
-      <c r="T15" s="61"/>
-      <c r="U15" s="62"/>
-      <c r="V15" s="62"/>
-    </row>
-    <row r="16" spans="1:22" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A16" s="18">
-        <v>10</v>
-      </c>
-      <c r="B16" s="23" t="s">
+      <c r="E16" s="11"/>
+      <c r="F16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="11"/>
+      <c r="N16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16" s="11"/>
+      <c r="P16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="57"/>
+    </row>
+    <row r="17" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="77">
+        <v>11</v>
+      </c>
+      <c r="B17" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="19" t="s">
+      <c r="C17" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="11"/>
+      <c r="J17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="15"/>
-      <c r="L16" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M16" s="15"/>
-      <c r="N16" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O16" s="15"/>
-      <c r="P16" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="56"/>
-    </row>
-    <row r="17" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
-        <v>11</v>
-      </c>
-      <c r="B17" s="24" t="s">
+      <c r="M17" s="11"/>
+      <c r="N17" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" s="15"/>
-      <c r="L17" s="19" t="s">
+      <c r="O17" s="11"/>
+      <c r="P17" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="61"/>
+    </row>
+    <row r="18" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="78">
+        <v>12</v>
+      </c>
+      <c r="B18" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="M17" s="15"/>
-      <c r="N17" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="O17" s="15"/>
-      <c r="P17" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="63" t="s">
+      <c r="E18" s="11"/>
+      <c r="F18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="11"/>
+      <c r="H18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="11"/>
+      <c r="J18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="11"/>
+      <c r="L18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" s="11"/>
+      <c r="N18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O18" s="11"/>
+      <c r="P18" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="60"/>
+      <c r="S18" s="61"/>
+    </row>
+    <row r="19" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="77">
+        <v>13</v>
+      </c>
+      <c r="B19" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="S17" s="64"/>
-    </row>
-    <row r="18" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A18" s="18">
-        <v>12</v>
-      </c>
-      <c r="B18" s="24" t="s">
+      <c r="C19" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="11"/>
+      <c r="H19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="11"/>
+      <c r="J19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="11"/>
+      <c r="L19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M19" s="11"/>
+      <c r="N19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O19" s="11"/>
+      <c r="P19" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="56"/>
+      <c r="S19" s="57"/>
+      <c r="Y19" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="19" t="s">
+    </row>
+    <row r="20" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="78">
+        <v>14</v>
+      </c>
+      <c r="B20" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="11"/>
+      <c r="H20" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" s="15"/>
-      <c r="N18" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O18" s="15"/>
-      <c r="P18" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="63"/>
-      <c r="S18" s="64"/>
-    </row>
-    <row r="19" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A19" s="11">
-        <v>13</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="15"/>
-      <c r="L19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" s="15"/>
-      <c r="N19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O19" s="15"/>
-      <c r="P19" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q19" s="29"/>
-      <c r="R19" s="55"/>
-      <c r="S19" s="56"/>
-      <c r="Y19" t="s">
+      <c r="I20" s="11"/>
+      <c r="J20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="11"/>
+      <c r="L20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="11"/>
+      <c r="N20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O20" s="11"/>
+      <c r="P20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="56"/>
+      <c r="S20" s="57"/>
+    </row>
+    <row r="21" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="77">
+        <v>15</v>
+      </c>
+      <c r="B21" s="75" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="20" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A20" s="18">
-        <v>14</v>
-      </c>
-      <c r="B20" s="30" t="s">
+      <c r="C21" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="11"/>
+      <c r="J21" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" s="11"/>
+      <c r="N21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O21" s="11"/>
+      <c r="P21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="56"/>
+      <c r="S21" s="57"/>
+    </row>
+    <row r="22" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="78">
+        <v>16</v>
+      </c>
+      <c r="B22" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="19" t="s">
+      <c r="C22" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="15"/>
-      <c r="J20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20" s="15"/>
-      <c r="L20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" s="15"/>
-      <c r="N20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O20" s="15"/>
-      <c r="P20" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="55"/>
-      <c r="S20" s="56"/>
-    </row>
-    <row r="21" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A21" s="11">
-        <v>15</v>
-      </c>
-      <c r="B21" s="12" t="s">
+      <c r="G22" s="11"/>
+      <c r="H22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="11"/>
+      <c r="J22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="11"/>
+      <c r="L22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="11"/>
+      <c r="N22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O22" s="11"/>
+      <c r="P22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="57"/>
+    </row>
+    <row r="23" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="77">
+        <v>17</v>
+      </c>
+      <c r="B23" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" s="15"/>
-      <c r="J21" s="19" t="s">
+      <c r="C23" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="15"/>
-      <c r="L21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" s="15"/>
-      <c r="N21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O21" s="15"/>
-      <c r="P21" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q21" s="29"/>
-      <c r="R21" s="55"/>
-      <c r="S21" s="56"/>
-    </row>
-    <row r="22" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A22" s="18">
-        <v>16</v>
-      </c>
-      <c r="B22" s="12" t="s">
+      <c r="I23" s="11"/>
+      <c r="J23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="11"/>
+      <c r="L23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23" s="11"/>
+      <c r="N23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O23" s="11"/>
+      <c r="P23" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="56"/>
+      <c r="S23" s="57"/>
+    </row>
+    <row r="24" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="78">
+        <v>18</v>
+      </c>
+      <c r="B24" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="19" t="s">
+      <c r="C24" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="11"/>
+      <c r="J24" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" s="15"/>
-      <c r="J22" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22" s="15"/>
-      <c r="L22" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M22" s="15"/>
-      <c r="N22" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O22" s="15"/>
-      <c r="P22" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q22" s="29"/>
-      <c r="R22" s="55"/>
-      <c r="S22" s="56"/>
-    </row>
-    <row r="23" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A23" s="11">
-        <v>17</v>
-      </c>
-      <c r="B23" s="12" t="s">
+      <c r="K24" s="11"/>
+      <c r="L24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" s="11"/>
+      <c r="N24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O24" s="11"/>
+      <c r="P24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="56"/>
+      <c r="S24" s="57"/>
+    </row>
+    <row r="25" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="77">
+        <v>19</v>
+      </c>
+      <c r="B25" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="19" t="s">
+      <c r="C25" s="81" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K23" s="15"/>
-      <c r="L23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O23" s="15"/>
-      <c r="P23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="55"/>
-      <c r="S23" s="56"/>
-    </row>
-    <row r="24" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A24" s="18">
-        <v>18</v>
-      </c>
-      <c r="B24" s="12" t="s">
+      <c r="G25" s="11"/>
+      <c r="H25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="11"/>
+      <c r="L25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M25" s="11"/>
+      <c r="N25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O25" s="11"/>
+      <c r="P25" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="41"/>
+    </row>
+    <row r="26" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A26" s="21"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="56"/>
+      <c r="S26" s="57"/>
+    </row>
+    <row r="27" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="22"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="63"/>
+      <c r="S27" s="64"/>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A28" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I24" s="15"/>
-      <c r="J24" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="K24" s="15"/>
-      <c r="L24" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M24" s="15"/>
-      <c r="N24" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O24" s="15"/>
-      <c r="P24" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="55"/>
-      <c r="S24" s="56"/>
-    </row>
-    <row r="25" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A25" s="11">
-        <v>19</v>
-      </c>
-      <c r="B25" s="31" t="s">
+      <c r="C28" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="15"/>
-      <c r="H25" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I25" s="15"/>
-      <c r="J25" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="K25" s="15"/>
-      <c r="L25" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O25" s="15"/>
-      <c r="P25" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q25" s="29"/>
-      <c r="R25" s="26"/>
-      <c r="S25" s="27"/>
-    </row>
-    <row r="26" spans="1:25" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A26" s="33"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="55"/>
-      <c r="S26" s="56"/>
-    </row>
-    <row r="27" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="39"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="37"/>
-      <c r="P27" s="37"/>
-      <c r="Q27" s="37"/>
-      <c r="R27" s="55"/>
-      <c r="S27" s="56"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A28" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="42"/>
+      <c r="K28" s="65"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="28"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="44"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="30"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
+      <c r="A29" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="M29" s="29"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="43" t="s">
+      <c r="R29" s="29"/>
+      <c r="S29" s="30"/>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="M29" s="43"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="3" t="s">
+      <c r="C30" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="R29" s="43"/>
-      <c r="S29" s="44"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A30" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="41" t="s">
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="31"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="R30" s="31"/>
+      <c r="S30" s="30"/>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" s="45"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45" t="s">
+      <c r="B31" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="R30" s="45"/>
-      <c r="S30" s="44"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A31" s="40" t="s">
+      <c r="C31" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28"/>
+      <c r="P31" s="28"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="33"/>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C32" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="46"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="59"/>
-      <c r="L31" s="59"/>
-      <c r="M31" s="59"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="45"/>
-      <c r="S31" s="47"/>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A32" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B32" s="41" t="s">
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="33"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="34"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="41" t="s">
+      <c r="D33" s="66"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28"/>
+      <c r="P33" s="28"/>
+      <c r="Q33" s="28"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="33"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="35"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28"/>
+      <c r="P34" s="28"/>
+      <c r="Q34" s="28"/>
+      <c r="R34" s="31"/>
+      <c r="S34" s="33"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="47"/>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="48"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="47"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="49"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="60"/>
-      <c r="D34" s="60"/>
-      <c r="E34" s="60"/>
-      <c r="F34" s="46"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="47"/>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="42"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="46"/>
-      <c r="G35" s="46"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="42"/>
-      <c r="K35" s="42"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="42"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="42"/>
-      <c r="P35" s="42"/>
-      <c r="Q35" s="42"/>
-      <c r="R35" s="45"/>
-      <c r="S35" s="47"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
+      <c r="R35" s="31"/>
+      <c r="S35" s="33"/>
     </row>
     <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="50"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="51"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="51"/>
-      <c r="M36" s="51"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="53"/>
-      <c r="S36" s="54"/>
+      <c r="A36" s="36"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="37"/>
+      <c r="M36" s="37"/>
+      <c r="N36" s="37"/>
+      <c r="O36" s="37"/>
+      <c r="P36" s="37"/>
+      <c r="Q36" s="37"/>
+      <c r="R36" s="39"/>
+      <c r="S36" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="R14:S14"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="R5:S6"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="R19:S19"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
-    <mergeCell ref="R13:S13"/>
-    <mergeCell ref="R15:S15"/>
     <mergeCell ref="T15:V15"/>
     <mergeCell ref="R16:S16"/>
     <mergeCell ref="R17:S17"/>
@@ -2592,7 +2623,42 @@
     <mergeCell ref="C30:E30"/>
     <mergeCell ref="K31:M31"/>
     <mergeCell ref="C33:E33"/>
+    <mergeCell ref="R19:S19"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="R14:S14"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="R5:S6"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>